--- a/artfynd/A 20931-2025 artfynd.xlsx
+++ b/artfynd/A 20931-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126017341</v>
       </c>
       <c r="B3" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20931-2025 artfynd.xlsx
+++ b/artfynd/A 20931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017347</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017341</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017345</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20931-2025 artfynd.xlsx
+++ b/artfynd/A 20931-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126017341</v>
       </c>
       <c r="B3" t="n">
-        <v>98372</v>
+        <v>98373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20931-2025 artfynd.xlsx
+++ b/artfynd/A 20931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017347</v>
       </c>
       <c r="B2" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017341</v>
       </c>
       <c r="B3" t="n">
-        <v>98373</v>
+        <v>98375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017345</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20931-2025 artfynd.xlsx
+++ b/artfynd/A 20931-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126017341</v>
       </c>
       <c r="B3" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20931-2025 artfynd.xlsx
+++ b/artfynd/A 20931-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126017341</v>
       </c>
       <c r="B3" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20931-2025 artfynd.xlsx
+++ b/artfynd/A 20931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017347</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017341</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98383</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017345</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 20931-2025 artfynd.xlsx
+++ b/artfynd/A 20931-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126017341</v>
       </c>
       <c r="B3" t="n">
-        <v>98383</v>
+        <v>98386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20931-2025 artfynd.xlsx
+++ b/artfynd/A 20931-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126017347</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126017341</v>
       </c>
       <c r="B3" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126017345</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
